--- a/03_Outputs/Bioenergetica_Norte/02_Demografia/demografia.xlsx
+++ b/03_Outputs/Bioenergetica_Norte/02_Demografia/demografia.xlsx
@@ -10,6 +10,11 @@
     <sheet name="estructura_edad" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="natalidad_mortalidad" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="migracion" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="_fig_01" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="_fig_02" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="_fig_03" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="_fig_04" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="_fig_05" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
@@ -675,31 +680,31 @@
         </is>
       </c>
       <c r="E2" s="4">
-        <v>12190</v>
+        <v>12511</v>
       </c>
       <c r="F2" s="10">
-        <v>0.0685748360166965</v>
+        <v>0.0712926239970824</v>
       </c>
       <c r="G2" s="6">
-        <v>3439</v>
+        <v>3144</v>
       </c>
       <c r="H2" s="12">
-        <v>0.282116488925349</v>
+        <v>0.251298857005835</v>
       </c>
       <c r="I2" s="14">
-        <v>0.0393221811861829</v>
+        <v>0.0393738259236068</v>
       </c>
       <c r="J2" s="8">
-        <v>8751</v>
+        <v>9367</v>
       </c>
       <c r="K2" s="16">
-        <v>0.717883511074651</v>
+        <v>0.748701142994165</v>
       </c>
       <c r="L2" s="18">
-        <v>0.0969049332816566</v>
+        <v>0.0979422405320061</v>
       </c>
       <c r="M2" s="20">
-        <v>35.9941142211827</v>
+        <v>36.9419493864821</v>
       </c>
     </row>
     <row r="3">
@@ -722,31 +727,31 @@
         </is>
       </c>
       <c r="E3" s="4">
-        <v>19812</v>
+        <v>21035</v>
       </c>
       <c r="F3" s="10">
-        <v>0.111452391399737</v>
+        <v>0.119865745805981</v>
       </c>
       <c r="G3" s="6">
-        <v>9469</v>
+        <v>9307</v>
       </c>
       <c r="H3" s="12">
-        <v>0.477942661013527</v>
+        <v>0.442453054433088</v>
       </c>
       <c r="I3" s="14">
-        <v>0.108270350000572</v>
+        <v>0.116556042579837</v>
       </c>
       <c r="J3" s="8">
-        <v>10343</v>
+        <v>11728</v>
       </c>
       <c r="K3" s="16">
-        <v>0.522057338986473</v>
+        <v>0.557546945566912</v>
       </c>
       <c r="L3" s="18">
-        <v>0.114534078954654</v>
+        <v>0.122629080491018</v>
       </c>
       <c r="M3" s="20">
-        <v>14.0135381685672</v>
+        <v>14.8785975860999</v>
       </c>
     </row>
     <row r="4">
@@ -769,31 +774,31 @@
         </is>
       </c>
       <c r="E4" s="4">
-        <v>8599</v>
+        <v>7957</v>
       </c>
       <c r="F4" s="10">
-        <v>0.0483736681630495</v>
+        <v>0.0453421316557257</v>
       </c>
       <c r="G4" s="6">
-        <v>3329</v>
+        <v>2808</v>
       </c>
       <c r="H4" s="12">
-        <v>0.387138039306896</v>
+        <v>0.352896820409702</v>
       </c>
       <c r="I4" s="14">
-        <v>0.0380644202293699</v>
+        <v>0.0351659361302442</v>
       </c>
       <c r="J4" s="8">
-        <v>5270</v>
+        <v>5149</v>
       </c>
       <c r="K4" s="16">
-        <v>0.612861960693104</v>
+        <v>0.647103179590298</v>
       </c>
       <c r="L4" s="18">
-        <v>0.0583577874979237</v>
+        <v>0.0538384324222589</v>
       </c>
       <c r="M4" s="20">
-        <v>22.8486093287861</v>
+        <v>21.1427357168451</v>
       </c>
     </row>
     <row r="5">
@@ -816,31 +821,31 @@
         </is>
       </c>
       <c r="E5" s="4">
-        <v>9839</v>
+        <v>10005</v>
       </c>
       <c r="F5" s="10">
-        <v>0.0553492872492434</v>
+        <v>0.0570124452954048</v>
       </c>
       <c r="G5" s="6">
-        <v>3310</v>
+        <v>3029</v>
       </c>
       <c r="H5" s="12">
-        <v>0.336416302469763</v>
+        <v>0.302748625687156</v>
       </c>
       <c r="I5" s="14">
-        <v>0.0378471706095567</v>
+        <v>0.0379336255479023</v>
       </c>
       <c r="J5" s="8">
-        <v>6529</v>
+        <v>6976</v>
       </c>
       <c r="K5" s="16">
-        <v>0.663583697530237</v>
+        <v>0.697251374312844</v>
       </c>
       <c r="L5" s="18">
-        <v>0.0722994297104258</v>
+        <v>0.0729417177272632</v>
       </c>
       <c r="M5" s="20">
-        <v>47.6826618872411</v>
+        <v>48.487146273183</v>
       </c>
     </row>
     <row r="6">
@@ -863,31 +868,31 @@
         </is>
       </c>
       <c r="E6" s="4">
-        <v>4242</v>
+        <v>3942</v>
       </c>
       <c r="F6" s="10">
-        <v>0.0238633678738988</v>
+        <v>0.0224630743982495</v>
       </c>
       <c r="G6" s="6">
-        <v>3323</v>
+        <v>2988</v>
       </c>
       <c r="H6" s="12">
-        <v>0.783356907119283</v>
+        <v>0.757990867579909</v>
       </c>
       <c r="I6" s="14">
-        <v>0.037995815086271</v>
+        <v>0.0374201628052599</v>
       </c>
       <c r="J6" s="8">
-        <v>919</v>
+        <v>954</v>
       </c>
       <c r="K6" s="16">
-        <v>0.216643092880717</v>
+        <v>0.242009132420091</v>
       </c>
       <c r="L6" s="18">
-        <v>0.0101766236642489</v>
+        <v>0.00997511449423869</v>
       </c>
       <c r="M6" s="20">
-        <v>28.3592512510528</v>
+        <v>26.353646494967</v>
       </c>
     </row>
     <row r="7">
@@ -910,31 +915,31 @@
         </is>
       </c>
       <c r="E7" s="4">
-        <v>10464</v>
+        <v>10373</v>
       </c>
       <c r="F7" s="10">
-        <v>0.0588652242886556</v>
+        <v>0.0591094547775346</v>
       </c>
       <c r="G7" s="6">
-        <v>5984</v>
+        <v>5578</v>
       </c>
       <c r="H7" s="12">
-        <v>0.571865443425077</v>
+        <v>0.537742215366818</v>
       </c>
       <c r="I7" s="14">
-        <v>0.0684221960506306</v>
+        <v>0.0698559799624296</v>
       </c>
       <c r="J7" s="8">
-        <v>4480</v>
+        <v>4795</v>
       </c>
       <c r="K7" s="16">
-        <v>0.428134556574924</v>
+        <v>0.462257784633182</v>
       </c>
       <c r="L7" s="18">
-        <v>0.0496096561652179</v>
+        <v>0.0501369748426358</v>
       </c>
       <c r="M7" s="20">
-        <v>31.4986581102055</v>
+        <v>31.224730559744</v>
       </c>
     </row>
     <row r="8">
@@ -957,31 +962,31 @@
         </is>
       </c>
       <c r="E8" s="4">
-        <v>7015</v>
+        <v>7009</v>
       </c>
       <c r="F8" s="10">
-        <v>0.0394628773303631</v>
+        <v>0.0399400528811087</v>
       </c>
       <c r="G8" s="6">
-        <v>2810</v>
+        <v>2562</v>
       </c>
       <c r="H8" s="12">
-        <v>0.400570206699929</v>
+        <v>0.365530032814952</v>
       </c>
       <c r="I8" s="14">
-        <v>0.0321300753513155</v>
+        <v>0.0320851596743895</v>
       </c>
       <c r="J8" s="8">
-        <v>4205</v>
+        <v>4447</v>
       </c>
       <c r="K8" s="16">
-        <v>0.599429793300071</v>
+        <v>0.634469967185048</v>
       </c>
       <c r="L8" s="18">
-        <v>0.046564420574719</v>
+        <v>0.0464982538321588</v>
       </c>
       <c r="M8" s="20">
-        <v>59.3445788448056</v>
+        <v>59.293820830113</v>
       </c>
     </row>
     <row r="9">
@@ -1004,31 +1009,31 @@
         </is>
       </c>
       <c r="E9" s="4">
-        <v>29074</v>
+        <v>29515</v>
       </c>
       <c r="F9" s="10">
-        <v>0.163555765574195</v>
+        <v>0.168188138220277</v>
       </c>
       <c r="G9" s="6">
-        <v>9265</v>
+        <v>8459</v>
       </c>
       <c r="H9" s="12">
-        <v>0.318669601705992</v>
+        <v>0.286600033881077</v>
       </c>
       <c r="I9" s="14">
-        <v>0.105937775135209</v>
+        <v>0.105936130244208</v>
       </c>
       <c r="J9" s="8">
-        <v>19809</v>
+        <v>21056</v>
       </c>
       <c r="K9" s="16">
-        <v>0.681330398294008</v>
+        <v>0.713399966118923</v>
       </c>
       <c r="L9" s="18">
-        <v>0.219356624771607</v>
+        <v>0.220163533323574</v>
       </c>
       <c r="M9" s="20">
-        <v>10.2333023711349</v>
+        <v>10.3885230612935</v>
       </c>
     </row>
     <row r="10">
@@ -1051,31 +1056,31 @@
         </is>
       </c>
       <c r="E10" s="4">
-        <v>7697</v>
+        <v>7402</v>
       </c>
       <c r="F10" s="10">
-        <v>0.0432994678277697</v>
+        <v>0.0421795222465354</v>
       </c>
       <c r="G10" s="6">
-        <v>3535</v>
+        <v>3139</v>
       </c>
       <c r="H10" s="12">
-        <v>0.45926984539431</v>
+        <v>0.424074574439341</v>
       </c>
       <c r="I10" s="14">
-        <v>0.0404198634757652</v>
+        <v>0.0393112085159674</v>
       </c>
       <c r="J10" s="8">
-        <v>4162</v>
+        <v>4263</v>
       </c>
       <c r="K10" s="16">
-        <v>0.54073015460569</v>
+        <v>0.575925425560659</v>
       </c>
       <c r="L10" s="18">
-        <v>0.0460882564642046</v>
+        <v>0.0445743323783433</v>
       </c>
       <c r="M10" s="20">
-        <v>35.1900484353504</v>
+        <v>33.8413327943957</v>
       </c>
     </row>
     <row r="11">
@@ -1098,31 +1103,31 @@
         </is>
       </c>
       <c r="E11" s="4">
-        <v>3941</v>
+        <v>4017</v>
       </c>
       <c r="F11" s="10">
-        <v>0.0221700925957179</v>
+        <v>0.02289045404814</v>
       </c>
       <c r="G11" s="6">
-        <v>2670</v>
+        <v>2599</v>
       </c>
       <c r="H11" s="12">
-        <v>0.677493022075615</v>
+        <v>0.647000248941996</v>
       </c>
       <c r="I11" s="14">
-        <v>0.030529288679008</v>
+        <v>0.0325485284909205</v>
       </c>
       <c r="J11" s="8">
-        <v>1271</v>
+        <v>1418</v>
       </c>
       <c r="K11" s="16">
-        <v>0.322506977924385</v>
+        <v>0.352999751058003</v>
       </c>
       <c r="L11" s="18">
-        <v>0.0140745252200875</v>
+        <v>0.014826742508208</v>
       </c>
       <c r="M11" s="20">
-        <v>31.2595222168032</v>
+        <v>31.8623447716058</v>
       </c>
     </row>
     <row r="12">
@@ -1145,31 +1150,31 @@
         </is>
       </c>
       <c r="E12" s="4">
-        <v>5296</v>
+        <v>4824</v>
       </c>
       <c r="F12" s="10">
-        <v>0.0297926440971636</v>
+        <v>0.0274890590809628</v>
       </c>
       <c r="G12" s="6">
-        <v>2115</v>
+        <v>1758</v>
       </c>
       <c r="H12" s="12">
-        <v>0.399358006042296</v>
+        <v>0.364427860696517</v>
       </c>
       <c r="I12" s="14">
-        <v>0.0241833129423602</v>
+        <v>0.0220162805259862</v>
       </c>
       <c r="J12" s="8">
-        <v>3181</v>
+        <v>3066</v>
       </c>
       <c r="K12" s="16">
-        <v>0.600641993957704</v>
+        <v>0.635572139303483</v>
       </c>
       <c r="L12" s="18">
-        <v>0.0352250705940978</v>
+        <v>0.0320583868336854</v>
       </c>
       <c r="M12" s="20">
-        <v>43.2049958680736</v>
+        <v>39.3543995595897</v>
       </c>
     </row>
     <row r="13">
@@ -1192,31 +1197,31 @@
         </is>
       </c>
       <c r="E13" s="4">
-        <v>14823</v>
+        <v>15014</v>
       </c>
       <c r="F13" s="10">
-        <v>0.0833867755763324</v>
+        <v>0.0855557075127644</v>
       </c>
       <c r="G13" s="6">
-        <v>4849</v>
+        <v>4414</v>
       </c>
       <c r="H13" s="12">
-        <v>0.327126762463739</v>
+        <v>0.293992273877714</v>
       </c>
       <c r="I13" s="14">
-        <v>0.0554443898144231</v>
+        <v>0.055278647463995</v>
       </c>
       <c r="J13" s="8">
-        <v>9974</v>
+        <v>10600</v>
       </c>
       <c r="K13" s="16">
-        <v>0.672873237536261</v>
+        <v>0.706007726122286</v>
       </c>
       <c r="L13" s="18">
-        <v>0.110447926471402</v>
+        <v>0.110834605491541</v>
       </c>
       <c r="M13" s="20">
-        <v>26.1105005684701</v>
+        <v>26.4469443118809</v>
       </c>
     </row>
     <row r="14">
@@ -1239,31 +1244,31 @@
         </is>
       </c>
       <c r="E14" s="4">
-        <v>44770</v>
+        <v>41884</v>
       </c>
       <c r="F14" s="10">
-        <v>0.251853602007178</v>
+        <v>0.238671590080233</v>
       </c>
       <c r="G14" s="6">
-        <v>33359</v>
+        <v>30065</v>
       </c>
       <c r="H14" s="12">
-        <v>0.745119499664954</v>
+        <v>0.717815872409512</v>
       </c>
       <c r="I14" s="14">
-        <v>0.381433161439336</v>
+        <v>0.376518472135254</v>
       </c>
       <c r="J14" s="8">
-        <v>11411</v>
+        <v>11819</v>
       </c>
       <c r="K14" s="16">
-        <v>0.254880500335046</v>
+        <v>0.282184127590488</v>
       </c>
       <c r="L14" s="18">
-        <v>0.126360666629755</v>
+        <v>0.123580585123068</v>
       </c>
       <c r="M14" s="20">
-        <v>60.6428990913185</v>
+        <v>56.7336874143575</v>
       </c>
     </row>
     <row r="15">
@@ -1288,31 +1293,31 @@
         </is>
       </c>
       <c r="E15" s="5">
-        <v>177762</v>
+        <v>175488</v>
       </c>
       <c r="F15" s="11">
         <v>1</v>
       </c>
       <c r="G15" s="7">
-        <v>87457</v>
+        <v>79850</v>
       </c>
       <c r="H15" s="13">
-        <v>0.491989289049403</v>
+        <v>0.455016867250182</v>
       </c>
       <c r="I15" s="15">
         <v>1</v>
       </c>
       <c r="J15" s="9">
-        <v>90305</v>
+        <v>95638</v>
       </c>
       <c r="K15" s="17">
-        <v>0.508010710950597</v>
+        <v>0.544983132749818</v>
       </c>
       <c r="L15" s="19">
         <v>1</v>
       </c>
       <c r="M15" s="21">
-        <v>23.5459478540759</v>
+        <v>23.2447390163031</v>
       </c>
     </row>
     <row r="16">
@@ -1337,7 +1342,7 @@
         </is>
       </c>
       <c r="E16" s="5">
-        <v>260133</v>
+        <v>255681</v>
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
@@ -1345,10 +1350,10 @@
         </is>
       </c>
       <c r="G16" s="7">
-        <v>138990</v>
+        <v>127611</v>
       </c>
       <c r="H16" s="13">
-        <v>0.534303606232197</v>
+        <v>0.499102397127671</v>
       </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
@@ -1356,10 +1361,10 @@
         </is>
       </c>
       <c r="J16" s="9">
-        <v>121143</v>
+        <v>128070</v>
       </c>
       <c r="K16" s="17">
-        <v>0.465696393767803</v>
+        <v>0.500897602872329</v>
       </c>
       <c r="L16" s="19" t="inlineStr">
         <is>
@@ -1367,7 +1372,7 @@
         </is>
       </c>
       <c r="M16" s="21">
-        <v>32.7821267437799</v>
+        <v>32.2210828613686</v>
       </c>
     </row>
     <row r="17">
@@ -1392,7 +1397,7 @@
         </is>
       </c>
       <c r="E17" s="5">
-        <v>6951825</v>
+        <v>6928372</v>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
@@ -1400,10 +1405,10 @@
         </is>
       </c>
       <c r="G17" s="7">
-        <v>5600952</v>
+        <v>5450720</v>
       </c>
       <c r="H17" s="13">
-        <v>0.80568081043467</v>
+        <v>0.786724500358814</v>
       </c>
       <c r="I17" s="15" t="inlineStr">
         <is>
@@ -1411,10 +1416,10 @@
         </is>
       </c>
       <c r="J17" s="9">
-        <v>1350873</v>
+        <v>1477652</v>
       </c>
       <c r="K17" s="17">
-        <v>0.19431918956533</v>
+        <v>0.213275499641186</v>
       </c>
       <c r="L17" s="19" t="inlineStr">
         <is>
@@ -1422,7 +1427,7 @@
         </is>
       </c>
       <c r="M17" s="21">
-        <v>110.689548218114</v>
+        <v>110.316120812453</v>
       </c>
     </row>
   </sheetData>
@@ -3578,13 +3583,13 @@
         </is>
       </c>
       <c r="E15" s="81">
-        <v>7.59862189387086</v>
+        <v>7.61066951537829</v>
       </c>
       <c r="F15" s="83">
-        <v>5.19483689736975</v>
+        <v>5.15478039829069</v>
       </c>
       <c r="G15" s="85">
-        <v>25.8773982891601</v>
+        <v>25.7972055824039</v>
       </c>
     </row>
     <row r="16">
@@ -3609,13 +3614,13 @@
         </is>
       </c>
       <c r="E16" s="81">
-        <v>7.91071129935279</v>
+        <v>7.88520580382868</v>
       </c>
       <c r="F16" s="83">
-        <v>5.17385870756554</v>
+        <v>5.13999885007764</v>
       </c>
       <c r="G16" s="85">
-        <v>26.4172625953481</v>
+        <v>26.3837840326381</v>
       </c>
     </row>
     <row r="17">
@@ -3640,13 +3645,13 @@
         </is>
       </c>
       <c r="E17" s="81">
-        <v>8.68409340580495</v>
+        <v>8.63819084562529</v>
       </c>
       <c r="F17" s="83">
-        <v>5.66384584790104</v>
+        <v>5.63888092494405</v>
       </c>
       <c r="G17" s="85">
-        <v>32.006905849399</v>
+        <v>32.052654940463</v>
       </c>
     </row>
   </sheetData>
@@ -4106,13 +4111,13 @@
         </is>
       </c>
       <c r="E15" s="87">
-        <v>1.46875697117534</v>
+        <v>1.44969519597397</v>
       </c>
       <c r="F15" s="89">
-        <v>1.48592593083259</v>
+        <v>1.47816073098033</v>
       </c>
       <c r="G15" s="91">
-        <v>1.5134787485471</v>
+        <v>1.47751310469842</v>
       </c>
     </row>
     <row r="16">
@@ -4137,13 +4142,13 @@
         </is>
       </c>
       <c r="E16" s="87">
-        <v>1.84401210131606</v>
+        <v>1.82462249111888</v>
       </c>
       <c r="F16" s="89">
-        <v>1.53308284269138</v>
+        <v>1.50531530154741</v>
       </c>
       <c r="G16" s="91">
-        <v>2.2588903797736</v>
+        <v>2.24897326039897</v>
       </c>
     </row>
     <row r="17">
@@ -4168,13 +4173,1173 @@
         </is>
       </c>
       <c r="E17" s="87">
-        <v>2.43831542235291</v>
+        <v>2.43784156596946</v>
       </c>
       <c r="F17" s="89">
-        <v>2.30723350389532</v>
+        <v>2.2991539975123</v>
       </c>
       <c r="G17" s="91">
-        <v>2.84838135541031</v>
+        <v>2.88568680338064</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>habitantes_total</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>part_total_prov</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>12511</v>
+      </c>
+      <c r="C2">
+        <v>0.0712926239970824</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>21035</v>
+      </c>
+      <c r="C3">
+        <v>0.119865745805981</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>7957</v>
+      </c>
+      <c r="C4">
+        <v>0.0453421316557257</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>10005</v>
+      </c>
+      <c r="C5">
+        <v>0.0570124452954048</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>3942</v>
+      </c>
+      <c r="C6">
+        <v>0.0224630743982495</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>10373</v>
+      </c>
+      <c r="C7">
+        <v>0.0591094547775346</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>7009</v>
+      </c>
+      <c r="C8">
+        <v>0.0399400528811087</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>29515</v>
+      </c>
+      <c r="C9">
+        <v>0.168188138220277</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>7402</v>
+      </c>
+      <c r="C10">
+        <v>0.0421795222465354</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>4017</v>
+      </c>
+      <c r="C11">
+        <v>0.02289045404814</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>4824</v>
+      </c>
+      <c r="C12">
+        <v>0.0274890590809628</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>15014</v>
+      </c>
+      <c r="C13">
+        <v>0.0855557075127644</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>41884</v>
+      </c>
+      <c r="C14">
+        <v>0.238671590080233</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="19.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>habitantes_cabecera</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>pct_cabecera</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>habitantes_rural</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>pct_rural</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>3144</v>
+      </c>
+      <c r="C2">
+        <v>0.251298857005835</v>
+      </c>
+      <c r="D2">
+        <v>9367</v>
+      </c>
+      <c r="E2">
+        <v>0.748701142994165</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>9307</v>
+      </c>
+      <c r="C3">
+        <v>0.442453054433088</v>
+      </c>
+      <c r="D3">
+        <v>11728</v>
+      </c>
+      <c r="E3">
+        <v>0.557546945566912</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>2808</v>
+      </c>
+      <c r="C4">
+        <v>0.352896820409702</v>
+      </c>
+      <c r="D4">
+        <v>5149</v>
+      </c>
+      <c r="E4">
+        <v>0.647103179590298</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>3029</v>
+      </c>
+      <c r="C5">
+        <v>0.302748625687156</v>
+      </c>
+      <c r="D5">
+        <v>6976</v>
+      </c>
+      <c r="E5">
+        <v>0.697251374312844</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>2988</v>
+      </c>
+      <c r="C6">
+        <v>0.757990867579909</v>
+      </c>
+      <c r="D6">
+        <v>954</v>
+      </c>
+      <c r="E6">
+        <v>0.242009132420091</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>5578</v>
+      </c>
+      <c r="C7">
+        <v>0.537742215366818</v>
+      </c>
+      <c r="D7">
+        <v>4795</v>
+      </c>
+      <c r="E7">
+        <v>0.462257784633182</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>2562</v>
+      </c>
+      <c r="C8">
+        <v>0.365530032814952</v>
+      </c>
+      <c r="D8">
+        <v>4447</v>
+      </c>
+      <c r="E8">
+        <v>0.634469967185048</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>8459</v>
+      </c>
+      <c r="C9">
+        <v>0.286600033881077</v>
+      </c>
+      <c r="D9">
+        <v>21056</v>
+      </c>
+      <c r="E9">
+        <v>0.713399966118923</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>3139</v>
+      </c>
+      <c r="C10">
+        <v>0.424074574439341</v>
+      </c>
+      <c r="D10">
+        <v>4263</v>
+      </c>
+      <c r="E10">
+        <v>0.575925425560659</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>2599</v>
+      </c>
+      <c r="C11">
+        <v>0.647000248941996</v>
+      </c>
+      <c r="D11">
+        <v>1418</v>
+      </c>
+      <c r="E11">
+        <v>0.352999751058003</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>1758</v>
+      </c>
+      <c r="C12">
+        <v>0.364427860696517</v>
+      </c>
+      <c r="D12">
+        <v>3066</v>
+      </c>
+      <c r="E12">
+        <v>0.635572139303483</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>4414</v>
+      </c>
+      <c r="C13">
+        <v>0.293992273877714</v>
+      </c>
+      <c r="D13">
+        <v>10600</v>
+      </c>
+      <c r="E13">
+        <v>0.706007726122286</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>30065</v>
+      </c>
+      <c r="C14">
+        <v>0.717815872409512</v>
+      </c>
+      <c r="D14">
+        <v>11819</v>
+      </c>
+      <c r="E14">
+        <v>0.282184127590488</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>habitantes_total</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>densidad_pob</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>12511</v>
+      </c>
+      <c r="C2">
+        <v>36.9419493864821</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>21035</v>
+      </c>
+      <c r="C3">
+        <v>14.8785975860999</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>7957</v>
+      </c>
+      <c r="C4">
+        <v>21.1427357168451</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>10005</v>
+      </c>
+      <c r="C5">
+        <v>48.487146273183</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>3942</v>
+      </c>
+      <c r="C6">
+        <v>26.353646494967</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>10373</v>
+      </c>
+      <c r="C7">
+        <v>31.224730559744</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>7009</v>
+      </c>
+      <c r="C8">
+        <v>59.293820830113</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>29515</v>
+      </c>
+      <c r="C9">
+        <v>10.3885230612935</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>7402</v>
+      </c>
+      <c r="C10">
+        <v>33.8413327943957</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>4017</v>
+      </c>
+      <c r="C11">
+        <v>31.8623447716058</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>4824</v>
+      </c>
+      <c r="C12">
+        <v>39.3543995595897</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>15014</v>
+      </c>
+      <c r="C13">
+        <v>26.4469443118809</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>41884</v>
+      </c>
+      <c r="C14">
+        <v>56.7336874143575</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:C19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="8.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>banda</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>sexo</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>personas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>0 a 9</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Hombres</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>14004</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>10 a 19</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Hombres</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>15127</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20 a 29</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Hombres</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>14433</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>30 a 39</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Hombres</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>15073</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>40 a 49</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Hombres</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>12163</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>50 a 59</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hombres</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>8918</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>60 a 69</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hombres</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>6961</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>70 a 79</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Hombres</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>3916</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>80 o más</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Hombres</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0 a 9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Mujeres</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>13726</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10 a 19</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Mujeres</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>14034</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20 a 29</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Mujeres</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>12532</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>30 a 39</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Mujeres</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>12963</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>40 a 49</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Mujeres</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>10515</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>50 a 59</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Mujeres</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>8585</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>60 a 69</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Mujeres</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>7223</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>70 a 79</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Mujeres</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>4138</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>80 o más</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Mujeres</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>1765</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1" gridLinesSet="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="22.711"/>
+    <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>I_enve_T</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Angostura</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>27.9622796227962</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>19.5797886053106</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Briceño</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>20.3905801263642</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Campamento</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>25.9169298032548</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Carolina del Príncipe</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>44.6200607902736</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gómez Plata</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>39.0018484288355</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Guadalupe</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>29.8931072613343</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Ituango</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>24.7091526819726</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>San Andrés de Cuerquía</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>24.4047619047619</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>San José de la Montaña</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>22.6389819156062</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Toledo</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>25.905547913801</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>20.6201033505584</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Yarumal</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>26.7033481620229</v>
       </c>
     </row>
   </sheetData>

--- a/03_Outputs/Bioenergetica_Norte/02_Demografia/demografia.xlsx
+++ b/03_Outputs/Bioenergetica_Norte/02_Demografia/demografia.xlsx
@@ -3583,7 +3583,7 @@
         </is>
       </c>
       <c r="E15" s="81">
-        <v>7.61066951537829</v>
+        <v>7.6106695153783</v>
       </c>
       <c r="F15" s="83">
         <v>5.15478039829069</v>
